--- a/data/2019_June_Sample.xlsx
+++ b/data/2019_June_Sample.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\Career\Git\biswaTemp\mess-list\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\Career\Git\mess-list\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -179,9 +179,6 @@
     <t>ESTABLISHE</t>
   </si>
   <si>
-    <t>DIDI</t>
-  </si>
-  <si>
     <t>GAS</t>
   </si>
   <si>
@@ -234,6 +231,9 @@
   </si>
   <si>
     <t>Mrinmoy</t>
+  </si>
+  <si>
+    <t>MASSI</t>
   </si>
 </sst>
 </file>
@@ -634,6 +634,12 @@
     <xf numFmtId="0" fontId="1" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -650,12 +656,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -968,16 +968,16 @@
         <v>42</v>
       </c>
       <c r="F1" s="9"/>
-      <c r="G1" s="48" t="s">
+      <c r="G1" s="42" t="s">
         <v>43</v>
       </c>
-      <c r="H1" s="48"/>
-      <c r="I1" s="48"/>
+      <c r="H1" s="42"/>
+      <c r="I1" s="42"/>
       <c r="K1" s="5"/>
-      <c r="L1" s="49" t="s">
+      <c r="L1" s="43" t="s">
         <v>44</v>
       </c>
-      <c r="M1" s="49"/>
+      <c r="M1" s="43"/>
     </row>
     <row r="3" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="4" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1024,7 +1024,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" s="33">
         <v>56</v>
@@ -1035,7 +1035,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C11" s="33">
         <v>40</v>
@@ -1046,7 +1046,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C12" s="16">
         <v>20</v>
@@ -1057,7 +1057,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C13" s="33">
         <v>50</v>
@@ -1068,7 +1068,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C14" s="33">
         <v>10</v>
@@ -1076,10 +1076,10 @@
     </row>
     <row r="15" spans="1:13" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="38" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C15" s="34">
         <v>44</v>
@@ -1125,7 +1125,7 @@
         <v>16</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
@@ -1133,7 +1133,7 @@
         <v>17</v>
       </c>
       <c r="B23" s="28" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
@@ -1141,7 +1141,7 @@
         <v>18</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
@@ -1149,15 +1149,15 @@
         <v>20</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="27" spans="1:15" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="42" t="s">
+      <c r="A27" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="B27" s="43"/>
+      <c r="B27" s="45"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="32" t="s">
@@ -1184,22 +1184,22 @@
       </c>
     </row>
     <row r="32" spans="1:15" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B32" s="44" t="s">
+      <c r="B32" s="46" t="s">
         <v>26</v>
       </c>
-      <c r="C32" s="44"/>
-      <c r="D32" s="44"/>
-      <c r="E32" s="44"/>
-      <c r="F32" s="44"/>
-      <c r="G32" s="44"/>
+      <c r="C32" s="46"/>
+      <c r="D32" s="46"/>
+      <c r="E32" s="46"/>
+      <c r="F32" s="46"/>
+      <c r="G32" s="46"/>
       <c r="H32" s="25"/>
-      <c r="K32" s="44" t="s">
+      <c r="K32" s="46" t="s">
         <v>27</v>
       </c>
-      <c r="L32" s="44"/>
-      <c r="M32" s="44"/>
-      <c r="N32" s="44"/>
-      <c r="O32" s="44"/>
+      <c r="L32" s="46"/>
+      <c r="M32" s="46"/>
+      <c r="N32" s="46"/>
+      <c r="O32" s="46"/>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
@@ -1300,10 +1300,10 @@
         <v>1</v>
       </c>
       <c r="K35" s="4">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="L35" s="4">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="M35" s="4">
         <v>0</v>
@@ -1390,7 +1390,7 @@
         <v>3</v>
       </c>
       <c r="K37" s="4">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L37" s="4">
         <v>0</v>
@@ -1435,10 +1435,10 @@
         <v>4</v>
       </c>
       <c r="K38" s="4">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="L38" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M38" s="4">
         <v>0</v>
@@ -1480,7 +1480,7 @@
         <v>5</v>
       </c>
       <c r="K39" s="4">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="L39" s="4">
         <v>0</v>
@@ -1525,7 +1525,7 @@
         <v>6</v>
       </c>
       <c r="K40" s="4">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="L40" s="4">
         <v>0</v>
@@ -1570,7 +1570,7 @@
         <v>7</v>
       </c>
       <c r="K41" s="4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L41" s="4">
         <v>0</v>
@@ -1615,7 +1615,7 @@
         <v>8</v>
       </c>
       <c r="K42" s="4">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L42" s="4">
         <v>0</v>
@@ -1660,7 +1660,7 @@
         <v>9</v>
       </c>
       <c r="K43" s="4">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="L43" s="4">
         <v>0</v>
@@ -1705,7 +1705,7 @@
         <v>10</v>
       </c>
       <c r="K44" s="4">
-        <v>0</v>
+        <v>290</v>
       </c>
       <c r="L44" s="4">
         <v>0</v>
@@ -1750,7 +1750,7 @@
         <v>11</v>
       </c>
       <c r="K45" s="4">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="L45" s="4">
         <v>0</v>
@@ -1779,7 +1779,7 @@
         <v>0</v>
       </c>
       <c r="D46" s="4">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="E46" s="4">
         <v>0</v>
@@ -1795,7 +1795,7 @@
         <v>12</v>
       </c>
       <c r="K46" s="4">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="L46" s="4">
         <v>0</v>
@@ -1843,7 +1843,7 @@
         <v>0</v>
       </c>
       <c r="L47" s="4">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="M47" s="4">
         <v>0</v>
@@ -1885,7 +1885,7 @@
         <v>14</v>
       </c>
       <c r="K48" s="4">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="L48" s="4">
         <v>0</v>
@@ -1975,7 +1975,7 @@
         <v>16</v>
       </c>
       <c r="K50" s="4">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L50" s="4">
         <v>0</v>
@@ -1987,7 +1987,7 @@
         <v>0</v>
       </c>
       <c r="O50" s="4">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="P50" s="4">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="C51" s="4">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="D51" s="4">
         <v>0</v>
@@ -2020,7 +2020,7 @@
         <v>17</v>
       </c>
       <c r="K51" s="4">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="L51" s="4">
         <v>0</v>
@@ -2065,7 +2065,7 @@
         <v>18</v>
       </c>
       <c r="K52" s="4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L52" s="4">
         <v>0</v>
@@ -2110,7 +2110,7 @@
         <v>19</v>
       </c>
       <c r="K53" s="4">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L53" s="4">
         <v>0</v>
@@ -2142,7 +2142,7 @@
         <v>0</v>
       </c>
       <c r="E54" s="4">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="F54" s="4">
         <v>0</v>
@@ -2155,10 +2155,10 @@
         <v>20</v>
       </c>
       <c r="K54" s="4">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="L54" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M54" s="4">
         <v>0</v>
@@ -2245,7 +2245,7 @@
         <v>22</v>
       </c>
       <c r="K56" s="4">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="L56" s="4">
         <v>0</v>
@@ -2280,7 +2280,7 @@
         <v>0</v>
       </c>
       <c r="F57" s="4">
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="G57" s="4">
         <v>0</v>
@@ -2290,10 +2290,10 @@
         <v>23</v>
       </c>
       <c r="K57" s="4">
-        <v>0</v>
+        <v>156</v>
       </c>
       <c r="L57" s="4">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="M57" s="4">
         <v>0</v>
@@ -2425,7 +2425,7 @@
         <v>26</v>
       </c>
       <c r="K60" s="4">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="L60" s="4">
         <v>0</v>
@@ -2470,13 +2470,13 @@
         <v>27</v>
       </c>
       <c r="K61" s="4">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L61" s="4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M61" s="4">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="N61" s="4">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>28</v>
       </c>
       <c r="K62" s="4">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L62" s="4">
         <v>0</v>
@@ -2560,7 +2560,7 @@
         <v>29</v>
       </c>
       <c r="K63" s="4">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="L63" s="4">
         <v>0</v>
@@ -2605,7 +2605,7 @@
         <v>30</v>
       </c>
       <c r="K64" s="4">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="L64" s="4">
         <v>0</v>
@@ -2645,22 +2645,22 @@
         <v>28</v>
       </c>
       <c r="B67" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="C67" s="27" t="s">
         <v>57</v>
       </c>
-      <c r="C67" s="27" t="s">
+      <c r="D67" s="27" t="s">
         <v>58</v>
       </c>
-      <c r="D67" s="27" t="s">
+      <c r="E67" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="E67" s="27" t="s">
+      <c r="F67" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="F67" s="27" t="s">
+      <c r="G67" s="27" t="s">
         <v>61</v>
-      </c>
-      <c r="G67" s="27" t="s">
-        <v>62</v>
       </c>
       <c r="H67" s="27"/>
       <c r="I67" s="24" t="s">
@@ -2670,7 +2670,7 @@
         <v>29</v>
       </c>
       <c r="K67" s="23" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="L67" s="23" t="s">
         <v>31</v>
@@ -2704,19 +2704,19 @@
       </c>
       <c r="C68" s="23">
         <f t="shared" si="0"/>
-        <v>200</v>
+        <v>1700</v>
       </c>
       <c r="D68" s="23">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="E68" s="23">
         <f t="shared" si="0"/>
-        <v>1500</v>
+        <v>2200</v>
       </c>
       <c r="F68" s="23">
         <f t="shared" si="0"/>
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="G68" s="27">
         <f t="shared" si="0"/>
@@ -2725,20 +2725,20 @@
       <c r="H68" s="30"/>
       <c r="I68" s="24">
         <f>SUM(B68:G68)</f>
-        <v>5200</v>
+        <v>11400</v>
       </c>
       <c r="J68" s="7"/>
       <c r="K68" s="7">
         <f>SUM(K35:K65)+K64</f>
-        <v>500</v>
+        <v>4861</v>
       </c>
       <c r="L68" s="7">
         <f t="shared" ref="L68:P68" si="1">SUM(L35:L65)</f>
-        <v>500</v>
+        <v>1600</v>
       </c>
       <c r="M68" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="N68" s="7">
         <f t="shared" si="1"/>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="O68" s="7">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="P68" s="8">
         <f t="shared" si="1"/>
@@ -2754,11 +2754,11 @@
       </c>
       <c r="Q68" s="24">
         <f>SUM(K68:P68)</f>
-        <v>1100</v>
+        <v>8061</v>
       </c>
       <c r="R68" s="24">
         <f>I68-Q68-H74</f>
-        <v>4100</v>
+        <v>3219</v>
       </c>
     </row>
     <row r="69" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
@@ -2768,22 +2768,22 @@
         <v>37</v>
       </c>
       <c r="B71" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="C71" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="C71" s="10" t="s">
+      <c r="D71" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="D71" s="10" t="s">
+      <c r="E71" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="E71" s="10" t="s">
+      <c r="F71" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="F71" s="10" t="s">
+      <c r="G71" s="10" t="s">
         <v>61</v>
-      </c>
-      <c r="G71" s="10" t="s">
-        <v>62</v>
       </c>
       <c r="H71" s="11" t="s">
         <v>40</v>
@@ -2823,13 +2823,13 @@
         <v>0</v>
       </c>
       <c r="C73" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D73" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E73" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F73" s="4">
         <v>0</v>
@@ -2851,15 +2851,15 @@
       </c>
       <c r="C74" s="7">
         <f>C72*H72+C73*H73</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D74" s="7">
         <f>D72*H72+D73*H73</f>
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="E74" s="23">
         <f>E72*H72+E73*H73</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F74" s="23">
         <f>F72*H72+F73*H73</f>
@@ -2871,46 +2871,46 @@
       </c>
       <c r="H74" s="41">
         <f>SUM(B74:G74)</f>
-        <v>0</v>
-      </c>
-      <c r="N74" s="45" t="s">
-        <v>56</v>
-      </c>
-      <c r="O74" s="45"/>
+        <v>120</v>
+      </c>
+      <c r="N74" s="47" t="s">
+        <v>55</v>
+      </c>
+      <c r="O74" s="47"/>
       <c r="P74" s="7">
         <f>(K68)/SUM(C10:C15)</f>
-        <v>2.2727272727272729</v>
+        <v>22.095454545454544</v>
       </c>
     </row>
     <row r="75" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="H75" s="13"/>
-      <c r="N75" s="45"/>
-      <c r="O75" s="45"/>
+      <c r="N75" s="47"/>
+      <c r="O75" s="47"/>
       <c r="P75" s="27"/>
     </row>
     <row r="76" spans="1:18" x14ac:dyDescent="0.3">
       <c r="M76" s="1"/>
-      <c r="N76" s="47"/>
-      <c r="O76" s="47"/>
-      <c r="P76" s="47"/>
+      <c r="N76" s="49"/>
+      <c r="O76" s="49"/>
+      <c r="P76" s="49"/>
     </row>
     <row r="77" spans="1:18" x14ac:dyDescent="0.3">
       <c r="M77" s="1"/>
-      <c r="N77" s="46"/>
-      <c r="O77" s="46"/>
-      <c r="P77" s="46"/>
+      <c r="N77" s="48"/>
+      <c r="O77" s="48"/>
+      <c r="P77" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="N75:O75"/>
+    <mergeCell ref="N77:P77"/>
+    <mergeCell ref="N76:P76"/>
+    <mergeCell ref="N74:O74"/>
     <mergeCell ref="G1:I1"/>
     <mergeCell ref="L1:M1"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="B32:G32"/>
     <mergeCell ref="K32:O32"/>
-    <mergeCell ref="N75:O75"/>
-    <mergeCell ref="N77:P77"/>
-    <mergeCell ref="N76:P76"/>
-    <mergeCell ref="N74:O74"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
